--- a/Project Docs/Sample BOM.xlsx
+++ b/Project Docs/Sample BOM.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="631">
   <si>
     <t>Level</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>Quoted</t>
+  </si>
+  <si>
+    <t>Country of Origin</t>
   </si>
   <si>
     <t>310-Electrical SA</t>
@@ -2270,6 +2273,9 @@
       <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -2277,17 +2283,17 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -2301,7 +2307,7 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="4" t="b">
         <v>1</v>
@@ -2323,6 +2329,7 @@
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="2">
@@ -2330,20 +2337,20 @@
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2">
@@ -2354,14 +2361,14 @@
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S3" s="4" t="b">
         <v>1</v>
@@ -2389,6 +2396,7 @@
       <c r="AH3" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" s="4"/>
     </row>
     <row r="4">
       <c r="A4" s="2">
@@ -2396,20 +2404,20 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="2">
@@ -2420,14 +2428,14 @@
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S4" s="4" t="b">
         <v>1</v>
@@ -2455,6 +2463,7 @@
       <c r="AH4" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="2">
@@ -2462,20 +2471,20 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="2">
@@ -2486,14 +2495,14 @@
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S5" s="4" t="b">
         <v>1</v>
@@ -2521,6 +2530,7 @@
       <c r="AH5" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" s="4"/>
     </row>
     <row r="6">
       <c r="A6" s="2">
@@ -2528,20 +2538,20 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K6" s="2">
         <v>2.0</v>
@@ -2551,13 +2561,13 @@
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S6" s="4" t="b">
         <v>1</v>
@@ -2585,6 +2595,7 @@
       <c r="AH6" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="2">
@@ -2592,20 +2603,20 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K7" s="2">
         <v>2.0</v>
@@ -2615,13 +2626,13 @@
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S7" s="4" t="b">
         <v>1</v>
@@ -2649,6 +2660,7 @@
       <c r="AH7" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" s="4"/>
     </row>
     <row r="8">
       <c r="A8" s="2">
@@ -2656,20 +2668,20 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="2">
@@ -2680,14 +2692,14 @@
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S8" s="4" t="b">
         <v>1</v>
@@ -2715,6 +2727,7 @@
       <c r="AH8" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="2">
@@ -2722,20 +2735,20 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="1">
         <v>1.0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="2">
@@ -2746,14 +2759,14 @@
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S9" s="4" t="b">
         <v>1</v>
@@ -2781,6 +2794,7 @@
       <c r="AH9" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI9" s="4"/>
     </row>
     <row r="10">
       <c r="A10" s="2">
@@ -2788,20 +2802,20 @@
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K10" s="2">
         <v>2.0</v>
@@ -2811,14 +2825,14 @@
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S10" s="4" t="b">
         <v>1</v>
@@ -2835,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB10" s="4" t="b">
         <v>0</v>
@@ -2848,6 +2862,7 @@
       <c r="AH10" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="2">
@@ -2855,20 +2870,20 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="2">
@@ -2879,14 +2894,14 @@
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q11" s="3"/>
       <c r="R11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S11" s="4" t="b">
         <v>1</v>
@@ -2914,6 +2929,7 @@
       <c r="AH11" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="2">
@@ -2921,20 +2937,20 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="2">
@@ -2945,14 +2961,14 @@
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S12" s="4" t="b">
         <v>1</v>
@@ -2980,6 +2996,7 @@
       <c r="AH12" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="2">
@@ -2987,20 +3004,20 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K13" s="2">
         <v>3.0</v>
@@ -3010,14 +3027,14 @@
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q13" s="3"/>
       <c r="R13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S13" s="4" t="b">
         <v>1</v>
@@ -3045,6 +3062,7 @@
       <c r="AH13" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="2">
@@ -3052,22 +3070,22 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K14" s="2">
         <v>3.0</v>
@@ -3077,14 +3095,14 @@
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q14" s="3"/>
       <c r="R14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S14" s="4" t="b">
         <v>1</v>
@@ -3096,7 +3114,7 @@
       </c>
       <c r="W14" s="3"/>
       <c r="X14" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y14" s="3"/>
       <c r="Z14" s="4" t="b">
@@ -3114,6 +3132,7 @@
       <c r="AH14" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI14" s="4"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
@@ -3121,20 +3140,20 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="2">
@@ -3145,14 +3164,14 @@
       </c>
       <c r="M15" s="3"/>
       <c r="N15" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S15" s="4" t="b">
         <v>1</v>
@@ -3169,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB15" s="4" t="b">
         <v>0</v>
@@ -3182,6 +3201,7 @@
       <c r="AH15" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI15" s="4"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
@@ -3189,22 +3209,22 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="2">
@@ -3215,13 +3235,13 @@
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S16" s="4" t="b">
         <v>1</v>
@@ -3231,7 +3251,7 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y16" s="3"/>
       <c r="Z16" s="4" t="b">
@@ -3249,6 +3269,7 @@
       <c r="AH16" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI16" s="4"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
@@ -3256,20 +3277,20 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="2">
@@ -3280,13 +3301,13 @@
       </c>
       <c r="M17" s="3"/>
       <c r="N17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S17" s="4" t="b">
         <v>1</v>
@@ -3314,6 +3335,7 @@
       <c r="AH17" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI17" s="4"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
@@ -3321,20 +3343,20 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="2">
@@ -3345,14 +3367,14 @@
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S18" s="4" t="b">
         <v>1</v>
@@ -3380,6 +3402,7 @@
       <c r="AH18" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" s="4"/>
     </row>
     <row r="19">
       <c r="A19" s="2">
@@ -3387,20 +3410,20 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K19" s="2">
         <v>6.0</v>
@@ -3410,13 +3433,13 @@
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S19" s="4" t="b">
         <v>1</v>
@@ -3446,6 +3469,7 @@
       <c r="AH19" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI19" s="4"/>
     </row>
     <row r="20">
       <c r="A20" s="2">
@@ -3453,20 +3477,20 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K20" s="2">
         <v>3.0</v>
@@ -3476,13 +3500,13 @@
       </c>
       <c r="M20" s="3"/>
       <c r="N20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S20" s="4" t="b">
         <v>1</v>
@@ -3510,6 +3534,7 @@
       <c r="AH20" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI20" s="4"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
@@ -3517,20 +3542,20 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K21" s="2">
         <v>3.0</v>
@@ -3540,13 +3565,13 @@
       </c>
       <c r="M21" s="3"/>
       <c r="N21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S21" s="4" t="b">
         <v>1</v>
@@ -3574,6 +3599,7 @@
       <c r="AH21" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI21" s="4"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
@@ -3581,20 +3607,20 @@
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K22" s="2">
         <v>4.0</v>
@@ -3604,14 +3630,14 @@
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S22" s="4" t="b">
         <v>1</v>
@@ -3639,6 +3665,7 @@
       <c r="AH22" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI22" s="4"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
@@ -3646,20 +3673,20 @@
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="2">
@@ -3670,14 +3697,14 @@
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q23" s="3"/>
       <c r="R23" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S23" s="4" t="b">
         <v>1</v>
@@ -3705,6 +3732,7 @@
       <c r="AH23" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
@@ -3712,20 +3740,20 @@
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="2">
@@ -3736,14 +3764,14 @@
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S24" s="4" t="b">
         <v>1</v>
@@ -3771,6 +3799,7 @@
       <c r="AH24" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI24" s="4"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
@@ -3778,20 +3807,20 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="2">
@@ -3802,14 +3831,14 @@
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q25" s="3"/>
       <c r="R25" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S25" s="4" t="b">
         <v>1</v>
@@ -3837,6 +3866,7 @@
       <c r="AH25" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI25" s="4"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
@@ -3844,20 +3874,20 @@
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="2">
@@ -3868,14 +3898,14 @@
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S26" s="4" t="b">
         <v>1</v>
@@ -3892,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB26" s="4" t="b">
         <v>0</v>
@@ -3905,6 +3935,7 @@
       <c r="AH26" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI26" s="4"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
@@ -3912,20 +3943,20 @@
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="2">
@@ -3936,14 +3967,14 @@
       </c>
       <c r="M27" s="3"/>
       <c r="N27" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S27" s="4" t="b">
         <v>1</v>
@@ -3971,6 +4002,7 @@
       <c r="AH27" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI27" s="4"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
@@ -3978,20 +4010,20 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="2">
@@ -4002,14 +4034,14 @@
       </c>
       <c r="M28" s="3"/>
       <c r="N28" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S28" s="4" t="b">
         <v>1</v>
@@ -4037,6 +4069,7 @@
       <c r="AH28" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI28" s="4"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
@@ -4044,20 +4077,20 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="2">
@@ -4068,13 +4101,13 @@
       </c>
       <c r="M29" s="3"/>
       <c r="N29" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S29" s="4" t="b">
         <v>1</v>
@@ -4102,6 +4135,7 @@
       <c r="AH29" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI29" s="4"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
@@ -4109,20 +4143,20 @@
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K30" s="2">
         <v>4.0</v>
@@ -4132,14 +4166,14 @@
       </c>
       <c r="M30" s="3"/>
       <c r="N30" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S30" s="4" t="b">
         <v>1</v>
@@ -4167,6 +4201,7 @@
       <c r="AH30" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI30" s="4"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
@@ -4174,20 +4209,20 @@
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="2">
@@ -4198,14 +4233,14 @@
       </c>
       <c r="M31" s="3"/>
       <c r="N31" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S31" s="4" t="b">
         <v>1</v>
@@ -4233,6 +4268,7 @@
       <c r="AH31" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI31" s="4"/>
     </row>
     <row r="32">
       <c r="A32" s="2">
@@ -4240,20 +4276,20 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="2">
@@ -4264,14 +4300,14 @@
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S32" s="4" t="b">
         <v>1</v>
@@ -4299,6 +4335,7 @@
       <c r="AH32" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI32" s="4"/>
     </row>
     <row r="33">
       <c r="A33" s="2">
@@ -4306,20 +4343,20 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="2">
@@ -4330,14 +4367,14 @@
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S33" s="4" t="b">
         <v>1</v>
@@ -4365,6 +4402,7 @@
       <c r="AH33" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI33" s="4"/>
     </row>
     <row r="34">
       <c r="A34" s="2">
@@ -4372,20 +4410,20 @@
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="2">
@@ -4396,13 +4434,13 @@
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S34" s="4" t="b">
         <v>1</v>
@@ -4430,6 +4468,7 @@
       <c r="AH34" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI34" s="4"/>
     </row>
     <row r="35">
       <c r="A35" s="2">
@@ -4437,20 +4476,20 @@
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K35" s="2">
         <v>11.0</v>
@@ -4460,19 +4499,19 @@
       </c>
       <c r="M35" s="3"/>
       <c r="N35" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S35" s="4" t="b">
         <v>1</v>
@@ -4502,6 +4541,7 @@
       <c r="AH35" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI35" s="4"/>
     </row>
     <row r="36">
       <c r="A36" s="2">
@@ -4509,14 +4549,14 @@
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H36" s="1">
         <v>1.0</v>
@@ -4531,14 +4571,14 @@
       </c>
       <c r="M36" s="3"/>
       <c r="N36" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S36" s="4" t="b">
         <v>1</v>
@@ -4566,6 +4606,7 @@
       <c r="AH36" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI36" s="4"/>
     </row>
     <row r="37">
       <c r="A37" s="2">
@@ -4573,17 +4614,17 @@
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="2">
@@ -4594,14 +4635,14 @@
       </c>
       <c r="M37" s="3"/>
       <c r="N37" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S37" s="4" t="b">
         <v>1</v>
@@ -4618,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="AA37" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB37" s="4" t="b">
         <v>0</v>
@@ -4631,6 +4672,7 @@
       <c r="AH37" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI37" s="4"/>
     </row>
     <row r="38">
       <c r="A38" s="2">
@@ -4638,17 +4680,17 @@
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
@@ -4660,14 +4702,14 @@
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S38" s="4" t="b">
         <v>1</v>
@@ -4695,6 +4737,7 @@
       <c r="AH38" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI38" s="4"/>
     </row>
     <row r="39">
       <c r="A39" s="2">
@@ -4702,20 +4745,20 @@
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="2">
@@ -4726,14 +4769,14 @@
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S39" s="4" t="b">
         <v>1</v>
@@ -4761,6 +4804,7 @@
       <c r="AH39" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI39" s="4"/>
     </row>
     <row r="40">
       <c r="A40" s="2">
@@ -4768,20 +4812,20 @@
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="2">
@@ -4792,13 +4836,13 @@
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S40" s="4" t="b">
         <v>1</v>
@@ -4828,6 +4872,7 @@
       <c r="AH40" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI40" s="4"/>
     </row>
     <row r="41">
       <c r="A41" s="2">
@@ -4835,20 +4880,20 @@
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K41" s="2">
         <v>2.0</v>
@@ -4858,14 +4903,14 @@
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q41" s="3"/>
       <c r="R41" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S41" s="4" t="b">
         <v>1</v>
@@ -4893,6 +4938,7 @@
       <c r="AH41" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI41" s="4"/>
     </row>
     <row r="42">
       <c r="A42" s="2">
@@ -4900,20 +4946,20 @@
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="2">
@@ -4924,13 +4970,13 @@
       </c>
       <c r="M42" s="3"/>
       <c r="N42" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S42" s="4" t="b">
         <v>1</v>
@@ -4958,6 +5004,7 @@
       <c r="AH42" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI42" s="4"/>
     </row>
     <row r="43">
       <c r="A43" s="2">
@@ -4965,20 +5012,20 @@
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="2">
@@ -4989,19 +5036,19 @@
       </c>
       <c r="M43" s="3"/>
       <c r="N43" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S43" s="4" t="b">
         <v>1</v>
@@ -5020,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="AA43" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB43" s="4" t="b">
         <v>0</v>
@@ -5033,6 +5080,7 @@
       <c r="AH43" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI43" s="4"/>
     </row>
     <row r="44">
       <c r="A44" s="2">
@@ -5040,20 +5088,20 @@
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K44" s="2">
         <v>6.0</v>
@@ -5063,14 +5111,14 @@
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q44" s="3"/>
       <c r="R44" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S44" s="4" t="b">
         <v>1</v>
@@ -5098,6 +5146,7 @@
       <c r="AH44" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI44" s="4"/>
     </row>
     <row r="45">
       <c r="A45" s="2">
@@ -5105,20 +5154,20 @@
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="2">
@@ -5129,14 +5178,14 @@
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q45" s="3"/>
       <c r="R45" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S45" s="4" t="b">
         <v>1</v>
@@ -5164,6 +5213,7 @@
       <c r="AH45" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI45" s="4"/>
     </row>
     <row r="46">
       <c r="A46" s="2">
@@ -5171,20 +5221,20 @@
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="2">
@@ -5195,15 +5245,15 @@
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S46" s="4" t="b">
         <v>1</v>
@@ -5220,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="AA46" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB46" s="4" t="b">
         <v>0</v>
@@ -5233,6 +5283,7 @@
       <c r="AH46" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI46" s="4"/>
     </row>
     <row r="47">
       <c r="A47" s="2">
@@ -5240,20 +5291,20 @@
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K47" s="2">
         <v>3.0</v>
@@ -5263,19 +5314,19 @@
       </c>
       <c r="M47" s="3"/>
       <c r="N47" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S47" s="4" t="b">
         <v>1</v>
@@ -5305,6 +5356,7 @@
       <c r="AH47" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI47" s="4"/>
     </row>
     <row r="48">
       <c r="A48" s="2">
@@ -5312,20 +5364,20 @@
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K48" s="2">
         <v>3.0</v>
@@ -5335,13 +5387,13 @@
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S48" s="4" t="b">
         <v>1</v>
@@ -5369,6 +5421,7 @@
       <c r="AH48" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI48" s="4"/>
     </row>
     <row r="49">
       <c r="A49" s="2">
@@ -5376,20 +5429,20 @@
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K49" s="2">
         <v>2.0</v>
@@ -5399,14 +5452,14 @@
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q49" s="3"/>
       <c r="R49" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S49" s="4" t="b">
         <v>1</v>
@@ -5436,6 +5489,7 @@
       <c r="AH49" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI49" s="4"/>
     </row>
     <row r="50">
       <c r="A50" s="2">
@@ -5443,20 +5497,20 @@
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="2">
@@ -5467,14 +5521,14 @@
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q50" s="3"/>
       <c r="R50" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S50" s="4" t="b">
         <v>1</v>
@@ -5502,6 +5556,7 @@
       <c r="AH50" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI50" s="4"/>
     </row>
     <row r="51">
       <c r="A51" s="2">
@@ -5509,16 +5564,16 @@
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H51" s="1">
         <v>1.0</v>
@@ -5533,13 +5588,13 @@
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S51" s="4" t="b">
         <v>1</v>
@@ -5565,6 +5620,7 @@
       <c r="AH51" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI51" s="4"/>
     </row>
     <row r="52">
       <c r="A52" s="2">
@@ -5572,20 +5628,20 @@
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="2">
@@ -5596,14 +5652,14 @@
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q52" s="3"/>
       <c r="R52" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S52" s="4" t="b">
         <v>1</v>
@@ -5633,6 +5689,7 @@
       <c r="AH52" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI52" s="4"/>
     </row>
     <row r="53">
       <c r="A53" s="2">
@@ -5640,20 +5697,20 @@
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="2">
@@ -5664,14 +5721,14 @@
       </c>
       <c r="M53" s="3"/>
       <c r="N53" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q53" s="3"/>
       <c r="R53" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S53" s="4" t="b">
         <v>1</v>
@@ -5699,6 +5756,7 @@
       <c r="AH53" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI53" s="4"/>
     </row>
     <row r="54">
       <c r="A54" s="2">
@@ -5706,20 +5764,20 @@
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K54" s="2">
         <v>25.0</v>
@@ -5729,19 +5787,19 @@
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S54" s="4" t="b">
         <v>1</v>
@@ -5760,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="AA54" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB54" s="4" t="b">
         <v>0</v>
@@ -5773,6 +5831,7 @@
       <c r="AH54" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI54" s="4"/>
     </row>
     <row r="55">
       <c r="A55" s="2">
@@ -5780,20 +5839,20 @@
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="2">
@@ -5804,13 +5863,13 @@
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S55" s="4" t="b">
         <v>1</v>
@@ -5838,6 +5897,7 @@
       <c r="AH55" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI55" s="4"/>
     </row>
     <row r="56">
       <c r="A56" s="2">
@@ -5845,20 +5905,20 @@
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K56" s="2">
         <v>2.0</v>
@@ -5868,14 +5928,14 @@
       </c>
       <c r="M56" s="3"/>
       <c r="N56" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q56" s="3"/>
       <c r="R56" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S56" s="4" t="b">
         <v>1</v>
@@ -5903,6 +5963,7 @@
       <c r="AH56" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI56" s="4"/>
     </row>
     <row r="57">
       <c r="A57" s="2">
@@ -5910,20 +5971,20 @@
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="2">
@@ -5934,14 +5995,14 @@
       </c>
       <c r="M57" s="3"/>
       <c r="N57" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q57" s="3"/>
       <c r="R57" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S57" s="4" t="b">
         <v>1</v>
@@ -5969,6 +6030,7 @@
       <c r="AH57" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI57" s="4"/>
     </row>
     <row r="58">
       <c r="A58" s="2">
@@ -5976,20 +6038,20 @@
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="2">
@@ -6000,13 +6062,13 @@
       </c>
       <c r="M58" s="3"/>
       <c r="N58" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S58" s="4" t="b">
         <v>1</v>
@@ -6034,6 +6096,7 @@
       <c r="AH58" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI58" s="4"/>
     </row>
     <row r="59">
       <c r="A59" s="2">
@@ -6041,20 +6104,20 @@
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K59" s="2">
         <v>2.0</v>
@@ -6064,19 +6127,19 @@
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S59" s="4" t="b">
         <v>1</v>
@@ -6106,6 +6169,7 @@
       <c r="AH59" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI59" s="4"/>
     </row>
     <row r="60">
       <c r="A60" s="2">
@@ -6113,20 +6177,20 @@
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K60" s="2">
         <v>11.0</v>
@@ -6136,19 +6200,19 @@
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S60" s="4" t="b">
         <v>1</v>
@@ -6165,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="AA60" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB60" s="4" t="b">
         <v>0</v>
@@ -6178,6 +6242,7 @@
       <c r="AH60" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI60" s="4"/>
     </row>
     <row r="61">
       <c r="A61" s="2">
@@ -6185,20 +6250,20 @@
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="2">
@@ -6209,19 +6274,19 @@
       </c>
       <c r="M61" s="3"/>
       <c r="N61" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S61" s="4" t="b">
         <v>1</v>
@@ -6240,7 +6305,7 @@
         <v>0</v>
       </c>
       <c r="AA61" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB61" s="4" t="b">
         <v>0</v>
@@ -6253,6 +6318,7 @@
       <c r="AH61" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI61" s="4"/>
     </row>
     <row r="62">
       <c r="A62" s="2">
@@ -6260,20 +6326,20 @@
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K62" s="2">
         <v>4.0</v>
@@ -6283,19 +6349,19 @@
       </c>
       <c r="M62" s="3"/>
       <c r="N62" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S62" s="4" t="b">
         <v>1</v>
@@ -6323,6 +6389,7 @@
       <c r="AH62" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI62" s="4"/>
     </row>
     <row r="63">
       <c r="A63" s="2">
@@ -6330,20 +6397,20 @@
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K63" s="2">
         <v>2.0</v>
@@ -6353,13 +6420,13 @@
       </c>
       <c r="M63" s="3"/>
       <c r="N63" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R63" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S63" s="4" t="b">
         <v>1</v>
@@ -6387,6 +6454,7 @@
       <c r="AH63" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI63" s="4"/>
     </row>
     <row r="64">
       <c r="A64" s="2">
@@ -6394,22 +6462,22 @@
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K64" s="2">
         <v>2.0</v>
@@ -6419,13 +6487,13 @@
       </c>
       <c r="M64" s="3"/>
       <c r="N64" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S64" s="4" t="b">
         <v>1</v>
@@ -6435,7 +6503,7 @@
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
       <c r="X64" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y64" s="3"/>
       <c r="Z64" s="4" t="b">
@@ -6453,6 +6521,7 @@
       <c r="AH64" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI64" s="4"/>
     </row>
     <row r="65">
       <c r="A65" s="2">
@@ -6460,20 +6529,20 @@
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K65" s="2">
         <v>6.0</v>
@@ -6483,13 +6552,13 @@
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R65" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S65" s="4" t="b">
         <v>1</v>
@@ -6517,6 +6586,7 @@
       <c r="AH65" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI65" s="4"/>
     </row>
     <row r="66">
       <c r="A66" s="2">
@@ -6524,14 +6594,14 @@
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H66" s="1">
         <v>1.0</v>
@@ -6546,14 +6616,14 @@
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q66" s="3"/>
       <c r="R66" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S66" s="4" t="b">
         <v>1</v>
@@ -6581,6 +6651,7 @@
       <c r="AH66" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI66" s="4"/>
     </row>
     <row r="67">
       <c r="A67" s="2">
@@ -6588,20 +6659,20 @@
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K67" s="2">
         <v>3.0</v>
@@ -6611,14 +6682,14 @@
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q67" s="3"/>
       <c r="R67" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S67" s="4" t="b">
         <v>1</v>
@@ -6635,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="AA67" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB67" s="4" t="b">
         <v>0</v>
@@ -6648,6 +6719,7 @@
       <c r="AH67" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI67" s="4"/>
     </row>
     <row r="68">
       <c r="A68" s="2">
@@ -6655,20 +6727,20 @@
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K68" s="2">
         <v>2.0</v>
@@ -6678,14 +6750,14 @@
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q68" s="3"/>
       <c r="R68" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S68" s="4" t="b">
         <v>1</v>
@@ -6713,6 +6785,7 @@
       <c r="AH68" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI68" s="4"/>
     </row>
     <row r="69">
       <c r="A69" s="2">
@@ -6720,20 +6793,20 @@
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K69" s="2">
         <v>2.0</v>
@@ -6743,19 +6816,19 @@
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S69" s="4" t="b">
         <v>1</v>
@@ -6783,6 +6856,7 @@
       <c r="AH69" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI69" s="4"/>
     </row>
     <row r="70">
       <c r="A70" s="2">
@@ -6790,20 +6864,20 @@
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="2">
@@ -6814,14 +6888,14 @@
       </c>
       <c r="M70" s="3"/>
       <c r="N70" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q70" s="3"/>
       <c r="R70" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S70" s="4" t="b">
         <v>1</v>
@@ -6849,6 +6923,7 @@
       <c r="AH70" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI70" s="4"/>
     </row>
     <row r="71">
       <c r="A71" s="2">
@@ -6856,16 +6931,16 @@
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H71" s="1">
         <v>1.0</v>
@@ -6880,14 +6955,14 @@
       </c>
       <c r="M71" s="3"/>
       <c r="N71" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q71" s="3"/>
       <c r="R71" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S71" s="4" t="b">
         <v>1</v>
@@ -6913,6 +6988,7 @@
       <c r="AH71" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI71" s="4"/>
     </row>
     <row r="72">
       <c r="A72" s="2">
@@ -6920,20 +6996,20 @@
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K72" s="2">
         <v>2.0</v>
@@ -6943,19 +7019,19 @@
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S72" s="4" t="b">
         <v>1</v>
@@ -6972,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="AA72" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB72" s="4" t="b">
         <v>0</v>
@@ -6985,6 +7061,7 @@
       <c r="AH72" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI72" s="4"/>
     </row>
     <row r="73">
       <c r="A73" s="2">
@@ -6992,20 +7069,20 @@
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K73" s="2">
         <v>2.0</v>
@@ -7015,13 +7092,13 @@
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S73" s="4" t="b">
         <v>1</v>
@@ -7049,6 +7126,7 @@
       <c r="AH73" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI73" s="4"/>
     </row>
     <row r="74">
       <c r="A74" s="2">
@@ -7056,20 +7134,20 @@
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="2">
@@ -7080,19 +7158,19 @@
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S74" s="4" t="b">
         <v>1</v>
@@ -7109,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="AA74" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB74" s="4" t="b">
         <v>0</v>
@@ -7122,6 +7200,7 @@
       <c r="AH74" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI74" s="4"/>
     </row>
     <row r="75">
       <c r="A75" s="2">
@@ -7129,20 +7208,20 @@
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" s="2">
@@ -7153,14 +7232,14 @@
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q75" s="3"/>
       <c r="R75" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S75" s="4" t="b">
         <v>1</v>
@@ -7188,6 +7267,7 @@
       <c r="AH75" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI75" s="4"/>
     </row>
     <row r="76">
       <c r="A76" s="2">
@@ -7195,20 +7275,20 @@
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J76" s="3"/>
       <c r="K76" s="2">
@@ -7219,14 +7299,14 @@
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q76" s="3"/>
       <c r="R76" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S76" s="4" t="b">
         <v>1</v>
@@ -7243,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="AA76" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB76" s="4" t="b">
         <v>0</v>
@@ -7256,6 +7336,7 @@
       <c r="AH76" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI76" s="4"/>
     </row>
     <row r="77">
       <c r="A77" s="2">
@@ -7263,20 +7344,20 @@
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" s="2">
@@ -7287,19 +7368,19 @@
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S77" s="4" t="b">
         <v>1</v>
@@ -7327,6 +7408,7 @@
       <c r="AH77" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI77" s="4"/>
     </row>
     <row r="78">
       <c r="A78" s="2">
@@ -7334,20 +7416,20 @@
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K78" s="2">
         <v>36.0</v>
@@ -7357,19 +7439,19 @@
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S78" s="4" t="b">
         <v>1</v>
@@ -7386,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="AA78" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB78" s="4" t="b">
         <v>0</v>
@@ -7399,6 +7481,7 @@
       <c r="AH78" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI78" s="4"/>
     </row>
     <row r="79">
       <c r="A79" s="2">
@@ -7406,20 +7489,20 @@
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" s="2">
@@ -7430,14 +7513,14 @@
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q79" s="3"/>
       <c r="R79" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S79" s="4" t="b">
         <v>1</v>
@@ -7465,6 +7548,7 @@
       <c r="AH79" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI79" s="4"/>
     </row>
     <row r="80">
       <c r="A80" s="2">
@@ -7472,20 +7556,20 @@
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K80" s="2">
         <v>1.0</v>
@@ -7495,14 +7579,14 @@
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q80" s="3"/>
       <c r="R80" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S80" s="4" t="b">
         <v>1</v>
@@ -7530,6 +7614,7 @@
       <c r="AH80" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI80" s="4"/>
     </row>
     <row r="81">
       <c r="A81" s="2">
@@ -7537,20 +7622,20 @@
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J81" s="3"/>
       <c r="K81" s="2">
@@ -7561,14 +7646,14 @@
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q81" s="3"/>
       <c r="R81" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S81" s="4" t="b">
         <v>1</v>
@@ -7596,6 +7681,7 @@
       <c r="AH81" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI81" s="4"/>
     </row>
     <row r="82">
       <c r="A82" s="2">
@@ -7603,22 +7689,22 @@
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J82" s="3"/>
       <c r="K82" s="2">
@@ -7629,14 +7715,14 @@
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q82" s="3"/>
       <c r="R82" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S82" s="4" t="b">
         <v>1</v>
@@ -7646,7 +7732,7 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y82" s="3"/>
       <c r="Z82" s="4" t="b">
@@ -7664,6 +7750,7 @@
       <c r="AH82" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI82" s="4"/>
     </row>
     <row r="83">
       <c r="A83" s="2">
@@ -7671,20 +7758,20 @@
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="2">
@@ -7695,14 +7782,14 @@
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q83" s="3"/>
       <c r="R83" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S83" s="4" t="b">
         <v>1</v>
@@ -7732,6 +7819,7 @@
       <c r="AH83" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI83" s="4"/>
     </row>
     <row r="84">
       <c r="A84" s="2">
@@ -7739,20 +7827,20 @@
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="2">
@@ -7763,14 +7851,14 @@
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q84" s="3"/>
       <c r="R84" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S84" s="4" t="b">
         <v>1</v>
@@ -7798,6 +7886,7 @@
       <c r="AH84" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI84" s="4"/>
     </row>
     <row r="85">
       <c r="A85" s="2">
@@ -7805,20 +7894,20 @@
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J85" s="3"/>
       <c r="K85" s="2">
@@ -7829,14 +7918,14 @@
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q85" s="3"/>
       <c r="R85" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S85" s="4" t="b">
         <v>1</v>
@@ -7864,6 +7953,7 @@
       <c r="AH85" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI85" s="4"/>
     </row>
     <row r="86">
       <c r="A86" s="2">
@@ -7871,22 +7961,22 @@
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J86" s="3"/>
       <c r="K86" s="2">
@@ -7897,14 +7987,14 @@
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q86" s="3"/>
       <c r="R86" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S86" s="4" t="b">
         <v>1</v>
@@ -7914,7 +8004,7 @@
       <c r="V86" s="3"/>
       <c r="W86" s="3"/>
       <c r="X86" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y86" s="3"/>
       <c r="Z86" s="4" t="b">
@@ -7932,6 +8022,7 @@
       <c r="AH86" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI86" s="4"/>
     </row>
     <row r="87">
       <c r="A87" s="2">
@@ -7939,20 +8030,20 @@
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K87" s="2">
         <v>2.0</v>
@@ -7962,14 +8053,14 @@
       </c>
       <c r="M87" s="3"/>
       <c r="N87" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q87" s="3"/>
       <c r="R87" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S87" s="4" t="b">
         <v>1</v>
@@ -7997,6 +8088,7 @@
       <c r="AH87" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI87" s="4"/>
     </row>
     <row r="88">
       <c r="A88" s="2">
@@ -8004,20 +8096,20 @@
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J88" s="3"/>
       <c r="K88" s="2">
@@ -8028,13 +8120,13 @@
       </c>
       <c r="M88" s="3"/>
       <c r="N88" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S88" s="4" t="b">
         <v>1</v>
@@ -8062,6 +8154,7 @@
       <c r="AH88" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI88" s="4"/>
     </row>
     <row r="89">
       <c r="A89" s="2">
@@ -8069,20 +8162,20 @@
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J89" s="3"/>
       <c r="K89" s="2">
@@ -8093,14 +8186,14 @@
       </c>
       <c r="M89" s="3"/>
       <c r="N89" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q89" s="3"/>
       <c r="R89" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S89" s="4" t="b">
         <v>1</v>
@@ -8128,6 +8221,7 @@
       <c r="AH89" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI89" s="4"/>
     </row>
     <row r="90">
       <c r="A90" s="2">
@@ -8135,20 +8229,20 @@
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K90" s="2">
         <v>2.0</v>
@@ -8158,17 +8252,17 @@
       </c>
       <c r="M90" s="3"/>
       <c r="N90" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q90" s="3"/>
       <c r="R90" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S90" s="4" t="b">
         <v>1</v>
@@ -8196,6 +8290,7 @@
       <c r="AH90" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI90" s="4"/>
     </row>
     <row r="91">
       <c r="A91" s="2">
@@ -8203,20 +8298,20 @@
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K91" s="2">
         <v>2.0</v>
@@ -8226,19 +8321,19 @@
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S91" s="4" t="b">
         <v>1</v>
@@ -8266,6 +8361,7 @@
       <c r="AH91" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI91" s="4"/>
     </row>
     <row r="92">
       <c r="A92" s="2">
@@ -8273,20 +8369,20 @@
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K92" s="2">
         <v>11.0</v>
@@ -8296,14 +8392,14 @@
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q92" s="3"/>
       <c r="R92" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S92" s="4" t="b">
         <v>1</v>
@@ -8333,6 +8429,7 @@
       <c r="AH92" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI92" s="4"/>
     </row>
     <row r="93">
       <c r="A93" s="2">
@@ -8340,20 +8437,20 @@
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J93" s="3"/>
       <c r="K93" s="2">
@@ -8364,13 +8461,13 @@
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S93" s="4" t="b">
         <v>1</v>
@@ -8398,6 +8495,7 @@
       <c r="AH93" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI93" s="4"/>
     </row>
     <row r="94">
       <c r="A94" s="2">
@@ -8405,20 +8503,20 @@
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J94" s="3"/>
       <c r="K94" s="2">
@@ -8429,13 +8527,13 @@
       </c>
       <c r="M94" s="3"/>
       <c r="N94" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S94" s="4" t="b">
         <v>1</v>
@@ -8463,6 +8561,7 @@
       <c r="AH94" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI94" s="4"/>
     </row>
     <row r="95">
       <c r="A95" s="2">
@@ -8470,20 +8569,20 @@
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K95" s="2">
         <v>3.0</v>
@@ -8493,19 +8592,19 @@
       </c>
       <c r="M95" s="3"/>
       <c r="N95" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S95" s="4" t="b">
         <v>1</v>
@@ -8535,6 +8634,7 @@
       <c r="AH95" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI95" s="4"/>
     </row>
     <row r="96">
       <c r="A96" s="2">
@@ -8542,20 +8642,20 @@
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J96" s="3"/>
       <c r="K96" s="2">
@@ -8566,19 +8666,19 @@
       </c>
       <c r="M96" s="3"/>
       <c r="N96" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q96" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S96" s="4" t="b">
         <v>1</v>
@@ -8606,6 +8706,7 @@
       <c r="AH96" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI96" s="4"/>
     </row>
     <row r="97">
       <c r="A97" s="2">
@@ -8613,20 +8714,20 @@
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J97" s="3"/>
       <c r="K97" s="2">
@@ -8637,14 +8738,14 @@
       </c>
       <c r="M97" s="3"/>
       <c r="N97" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q97" s="3"/>
       <c r="R97" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S97" s="4" t="b">
         <v>1</v>
@@ -8661,7 +8762,7 @@
         <v>0</v>
       </c>
       <c r="AA97" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB97" s="4" t="b">
         <v>0</v>
@@ -8674,6 +8775,7 @@
       <c r="AH97" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI97" s="4"/>
     </row>
     <row r="98">
       <c r="A98" s="2">
@@ -8681,22 +8783,22 @@
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J98" s="3"/>
       <c r="K98" s="2">
@@ -8707,14 +8809,14 @@
       </c>
       <c r="M98" s="3"/>
       <c r="N98" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q98" s="3"/>
       <c r="R98" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S98" s="4" t="b">
         <v>1</v>
@@ -8724,7 +8826,7 @@
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
       <c r="X98" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y98" s="3"/>
       <c r="Z98" s="4" t="b">
@@ -8742,6 +8844,7 @@
       <c r="AH98" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI98" s="4"/>
     </row>
     <row r="99">
       <c r="A99" s="2">
@@ -8749,20 +8852,20 @@
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -8772,14 +8875,14 @@
       </c>
       <c r="M99" s="3"/>
       <c r="N99" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q99" s="3"/>
       <c r="R99" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S99" s="4" t="b">
         <v>1</v>
@@ -8807,6 +8910,7 @@
       <c r="AH99" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI99" s="4"/>
     </row>
     <row r="100">
       <c r="A100" s="2">
@@ -8814,20 +8918,20 @@
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J100" s="3"/>
       <c r="K100" s="2">
@@ -8838,14 +8942,14 @@
       </c>
       <c r="M100" s="3"/>
       <c r="N100" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Q100" s="3"/>
       <c r="R100" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S100" s="4" t="b">
         <v>1</v>
@@ -8873,6 +8977,7 @@
       <c r="AH100" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI100" s="4"/>
     </row>
     <row r="101">
       <c r="A101" s="2">
@@ -8880,20 +8985,20 @@
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J101" s="3"/>
       <c r="K101" s="2">
@@ -8904,13 +9009,13 @@
       </c>
       <c r="M101" s="3"/>
       <c r="N101" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S101" s="4" t="b">
         <v>1</v>
@@ -8940,6 +9045,7 @@
       <c r="AH101" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI101" s="4"/>
     </row>
     <row r="102">
       <c r="A102" s="2">
@@ -8947,20 +9053,20 @@
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J102" s="3"/>
       <c r="K102" s="2">
@@ -8971,14 +9077,14 @@
       </c>
       <c r="M102" s="3"/>
       <c r="N102" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O102" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q102" s="3"/>
       <c r="R102" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S102" s="4" t="b">
         <v>1</v>
@@ -9006,6 +9112,7 @@
       <c r="AH102" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI102" s="4"/>
     </row>
     <row r="103">
       <c r="A103" s="2">
@@ -9013,20 +9120,20 @@
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J103" s="3"/>
       <c r="K103" s="2">
@@ -9037,14 +9144,14 @@
       </c>
       <c r="M103" s="3"/>
       <c r="N103" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Q103" s="3"/>
       <c r="R103" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S103" s="4" t="b">
         <v>1</v>
@@ -9072,6 +9179,7 @@
       <c r="AH103" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI103" s="4"/>
     </row>
     <row r="104">
       <c r="A104" s="2">
@@ -9079,20 +9187,20 @@
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K104" s="2">
         <v>4.0</v>
@@ -9102,13 +9210,13 @@
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S104" s="4" t="b">
         <v>1</v>
@@ -9136,6 +9244,7 @@
       <c r="AH104" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI104" s="4"/>
     </row>
     <row r="105">
       <c r="A105" s="2">
@@ -9143,22 +9252,22 @@
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K105" s="2">
         <v>4.0</v>
@@ -9168,14 +9277,14 @@
       </c>
       <c r="M105" s="3"/>
       <c r="N105" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Q105" s="3"/>
       <c r="R105" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S105" s="4" t="b">
         <v>1</v>
@@ -9185,7 +9294,7 @@
       <c r="V105" s="3"/>
       <c r="W105" s="3"/>
       <c r="X105" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y105" s="3"/>
       <c r="Z105" s="4" t="b">
@@ -9203,6 +9312,7 @@
       <c r="AH105" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI105" s="4"/>
     </row>
     <row r="106">
       <c r="A106" s="2">
@@ -9210,20 +9320,20 @@
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J106" s="3"/>
       <c r="K106" s="2">
@@ -9234,14 +9344,14 @@
       </c>
       <c r="M106" s="3"/>
       <c r="N106" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Q106" s="3"/>
       <c r="R106" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S106" s="4" t="b">
         <v>1</v>
@@ -9258,7 +9368,7 @@
         <v>0</v>
       </c>
       <c r="AA106" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB106" s="4" t="b">
         <v>0</v>
@@ -9271,6 +9381,7 @@
       <c r="AH106" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI106" s="4"/>
     </row>
     <row r="107">
       <c r="A107" s="2">
@@ -9278,17 +9389,17 @@
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I107" s="3"/>
       <c r="J107" s="3"/>
@@ -9300,14 +9411,14 @@
       </c>
       <c r="M107" s="3"/>
       <c r="N107" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Q107" s="3"/>
       <c r="R107" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S107" s="4" t="b">
         <v>1</v>
@@ -9335,6 +9446,7 @@
       <c r="AH107" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI107" s="4"/>
     </row>
     <row r="108">
       <c r="A108" s="2">
@@ -9342,20 +9454,20 @@
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J108" s="3"/>
       <c r="K108" s="2">
@@ -9366,13 +9478,13 @@
       </c>
       <c r="M108" s="3"/>
       <c r="N108" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S108" s="4" t="b">
         <v>1</v>
@@ -9400,6 +9512,7 @@
       <c r="AH108" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI108" s="4"/>
     </row>
     <row r="109">
       <c r="A109" s="2">
@@ -9407,20 +9520,20 @@
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J109" s="3"/>
       <c r="K109" s="2">
@@ -9431,19 +9544,19 @@
       </c>
       <c r="M109" s="3"/>
       <c r="N109" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S109" s="4" t="b">
         <v>1</v>
@@ -9462,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="AA109" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB109" s="4" t="b">
         <v>0</v>
@@ -9475,6 +9588,7 @@
       <c r="AH109" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI109" s="4"/>
     </row>
     <row r="110">
       <c r="A110" s="2">
@@ -9482,20 +9596,20 @@
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K110" s="2">
         <v>2.0</v>
@@ -9505,19 +9619,19 @@
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S110" s="4" t="b">
         <v>1</v>
@@ -9545,6 +9659,7 @@
       <c r="AH110" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI110" s="4"/>
     </row>
     <row r="111">
       <c r="A111" s="2">
@@ -9552,20 +9667,20 @@
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K111" s="2">
         <v>3.0</v>
@@ -9575,14 +9690,14 @@
       </c>
       <c r="M111" s="3"/>
       <c r="N111" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Q111" s="3"/>
       <c r="R111" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S111" s="4" t="b">
         <v>1</v>
@@ -9610,6 +9725,7 @@
       <c r="AH111" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI111" s="4"/>
     </row>
     <row r="112">
       <c r="A112" s="2">
@@ -9617,20 +9733,20 @@
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J112" s="3"/>
       <c r="K112" s="2">
@@ -9641,13 +9757,13 @@
       </c>
       <c r="M112" s="3"/>
       <c r="N112" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S112" s="4" t="b">
         <v>1</v>
@@ -9675,6 +9791,7 @@
       <c r="AH112" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI112" s="4"/>
     </row>
     <row r="113">
       <c r="A113" s="2">
@@ -9682,20 +9799,20 @@
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="J113" s="3"/>
       <c r="K113" s="2">
@@ -9706,19 +9823,19 @@
       </c>
       <c r="M113" s="3"/>
       <c r="N113" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q113" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S113" s="4" t="b">
         <v>1</v>
@@ -9748,6 +9865,7 @@
       <c r="AH113" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI113" s="4"/>
     </row>
     <row r="114">
       <c r="A114" s="2">
@@ -9755,20 +9873,20 @@
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J114" s="3"/>
       <c r="K114" s="2">
@@ -9779,14 +9897,14 @@
       </c>
       <c r="M114" s="3"/>
       <c r="N114" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Q114" s="3"/>
       <c r="R114" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S114" s="4" t="b">
         <v>1</v>
@@ -9814,6 +9932,7 @@
       <c r="AH114" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI114" s="4"/>
     </row>
     <row r="115">
       <c r="A115" s="2">
@@ -9821,20 +9940,20 @@
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="J115" s="3"/>
       <c r="K115" s="2">
@@ -9845,14 +9964,14 @@
       </c>
       <c r="M115" s="3"/>
       <c r="N115" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Q115" s="3"/>
       <c r="R115" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S115" s="4" t="b">
         <v>1</v>
@@ -9880,6 +9999,7 @@
       <c r="AH115" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI115" s="4"/>
     </row>
     <row r="116">
       <c r="A116" s="2">
@@ -9887,20 +10007,20 @@
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K116" s="2">
         <v>2.0</v>
@@ -9910,14 +10030,14 @@
       </c>
       <c r="M116" s="3"/>
       <c r="N116" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O116" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q116" s="3"/>
       <c r="R116" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S116" s="4" t="b">
         <v>1</v>
@@ -9945,6 +10065,7 @@
       <c r="AH116" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI116" s="4"/>
     </row>
     <row r="117">
       <c r="A117" s="2">
@@ -9952,20 +10073,20 @@
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J117" s="3"/>
       <c r="K117" s="2">
@@ -9976,14 +10097,14 @@
       </c>
       <c r="M117" s="3"/>
       <c r="N117" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Q117" s="3"/>
       <c r="R117" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S117" s="4" t="b">
         <v>1</v>
@@ -10011,6 +10132,7 @@
       <c r="AH117" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI117" s="4"/>
     </row>
     <row r="118">
       <c r="A118" s="2">
@@ -10018,20 +10140,20 @@
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J118" s="3"/>
       <c r="K118" s="2">
@@ -10042,14 +10164,14 @@
       </c>
       <c r="M118" s="3"/>
       <c r="N118" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="Q118" s="3"/>
       <c r="R118" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S118" s="4" t="b">
         <v>1</v>
@@ -10077,6 +10199,7 @@
       <c r="AH118" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI118" s="4"/>
     </row>
     <row r="119">
       <c r="A119" s="2">
@@ -10084,22 +10207,22 @@
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J119" s="3"/>
       <c r="K119" s="2">
@@ -10110,14 +10233,14 @@
       </c>
       <c r="M119" s="3"/>
       <c r="N119" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Q119" s="3"/>
       <c r="R119" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S119" s="4" t="b">
         <v>1</v>
@@ -10127,7 +10250,7 @@
       <c r="V119" s="3"/>
       <c r="W119" s="3"/>
       <c r="X119" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y119" s="3"/>
       <c r="Z119" s="4" t="b">
@@ -10145,6 +10268,7 @@
       <c r="AH119" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI119" s="4"/>
     </row>
     <row r="120">
       <c r="A120" s="2">
@@ -10152,20 +10276,20 @@
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K120" s="2">
         <v>4.0</v>
@@ -10175,14 +10299,14 @@
       </c>
       <c r="M120" s="3"/>
       <c r="N120" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Q120" s="3"/>
       <c r="R120" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S120" s="4" t="b">
         <v>1</v>
@@ -10210,6 +10334,7 @@
       <c r="AH120" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI120" s="4"/>
     </row>
     <row r="121">
       <c r="A121" s="2">
@@ -10217,20 +10342,20 @@
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J121" s="3"/>
       <c r="K121" s="2">
@@ -10241,14 +10366,14 @@
       </c>
       <c r="M121" s="3"/>
       <c r="N121" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Q121" s="3"/>
       <c r="R121" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S121" s="4" t="b">
         <v>1</v>
@@ -10276,6 +10401,7 @@
       <c r="AH121" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI121" s="4"/>
     </row>
     <row r="122">
       <c r="A122" s="2">
@@ -10283,20 +10409,20 @@
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K122" s="2">
         <v>2.0</v>
@@ -10306,14 +10432,14 @@
       </c>
       <c r="M122" s="3"/>
       <c r="N122" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Q122" s="3"/>
       <c r="R122" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S122" s="4" t="b">
         <v>1</v>
@@ -10341,6 +10467,7 @@
       <c r="AH122" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI122" s="4"/>
     </row>
     <row r="123">
       <c r="A123" s="2">
@@ -10348,20 +10475,20 @@
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J123" s="3"/>
       <c r="K123" s="2">
@@ -10372,14 +10499,14 @@
       </c>
       <c r="M123" s="3"/>
       <c r="N123" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="Q123" s="3"/>
       <c r="R123" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S123" s="4" t="b">
         <v>1</v>
@@ -10407,6 +10534,7 @@
       <c r="AH123" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI123" s="4"/>
     </row>
     <row r="124">
       <c r="A124" s="2">
@@ -10414,20 +10542,20 @@
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J124" s="3"/>
       <c r="K124" s="2">
@@ -10438,13 +10566,13 @@
       </c>
       <c r="M124" s="3"/>
       <c r="N124" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S124" s="4" t="b">
         <v>1</v>
@@ -10472,6 +10600,7 @@
       <c r="AH124" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI124" s="4"/>
     </row>
     <row r="125">
       <c r="A125" s="2">
@@ -10479,20 +10608,20 @@
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J125" s="3"/>
       <c r="K125" s="2">
@@ -10503,14 +10632,14 @@
       </c>
       <c r="M125" s="3"/>
       <c r="N125" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O125" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Q125" s="3"/>
       <c r="R125" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S125" s="4" t="b">
         <v>1</v>
@@ -10538,6 +10667,7 @@
       <c r="AH125" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI125" s="4"/>
     </row>
     <row r="126">
       <c r="A126" s="2">
@@ -10545,20 +10675,20 @@
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K126" s="2">
         <v>2.0</v>
@@ -10568,14 +10698,14 @@
       </c>
       <c r="M126" s="3"/>
       <c r="N126" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O126" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Q126" s="3"/>
       <c r="R126" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S126" s="4" t="b">
         <v>1</v>
@@ -10603,6 +10733,7 @@
       <c r="AH126" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI126" s="4"/>
     </row>
     <row r="127">
       <c r="A127" s="2">
@@ -10610,20 +10741,20 @@
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K127" s="2">
         <v>23.0</v>
@@ -10633,19 +10764,19 @@
       </c>
       <c r="M127" s="3"/>
       <c r="N127" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O127" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q127" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="R127" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S127" s="4" t="b">
         <v>1</v>
@@ -10664,7 +10795,7 @@
         <v>0</v>
       </c>
       <c r="AA127" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB127" s="4" t="b">
         <v>0</v>
@@ -10677,6 +10808,7 @@
       <c r="AH127" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI127" s="4"/>
     </row>
     <row r="128">
       <c r="A128" s="2">
@@ -10684,20 +10816,20 @@
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K128" s="2">
         <v>6.0</v>
@@ -10707,14 +10839,14 @@
       </c>
       <c r="M128" s="3"/>
       <c r="N128" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O128" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Q128" s="3"/>
       <c r="R128" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S128" s="4" t="b">
         <v>1</v>
@@ -10742,6 +10874,7 @@
       <c r="AH128" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI128" s="4"/>
     </row>
     <row r="129">
       <c r="A129" s="2">
@@ -10749,20 +10882,20 @@
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="J129" s="3"/>
       <c r="K129" s="2">
@@ -10773,14 +10906,14 @@
       </c>
       <c r="M129" s="3"/>
       <c r="N129" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O129" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="Q129" s="3"/>
       <c r="R129" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S129" s="4" t="b">
         <v>1</v>
@@ -10808,6 +10941,7 @@
       <c r="AH129" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI129" s="4"/>
     </row>
     <row r="130">
       <c r="A130" s="2">
@@ -10815,20 +10949,20 @@
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J130" s="3"/>
       <c r="K130" s="2">
@@ -10839,14 +10973,14 @@
       </c>
       <c r="M130" s="3"/>
       <c r="N130" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O130" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="Q130" s="3"/>
       <c r="R130" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S130" s="4" t="b">
         <v>1</v>
@@ -10863,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="AA130" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AB130" s="4" t="b">
         <v>0</v>
@@ -10876,6 +11010,7 @@
       <c r="AH130" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI130" s="4"/>
     </row>
     <row r="131">
       <c r="A131" s="2">
@@ -10883,20 +11018,20 @@
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K131" s="2">
         <v>9.0</v>
@@ -10906,19 +11041,19 @@
       </c>
       <c r="M131" s="3"/>
       <c r="N131" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O131" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P131" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q131" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S131" s="4" t="b">
         <v>1</v>
@@ -10948,6 +11083,7 @@
       <c r="AH131" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI131" s="4"/>
     </row>
     <row r="132">
       <c r="A132" s="2">
@@ -10955,22 +11091,22 @@
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K132" s="2">
         <v>9.0</v>
@@ -10980,13 +11116,13 @@
       </c>
       <c r="M132" s="3"/>
       <c r="N132" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O132" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S132" s="4" t="b">
         <v>1</v>
@@ -10996,7 +11132,7 @@
       <c r="V132" s="3"/>
       <c r="W132" s="3"/>
       <c r="X132" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y132" s="3"/>
       <c r="Z132" s="4" t="b">
@@ -11014,6 +11150,7 @@
       <c r="AH132" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI132" s="4"/>
     </row>
     <row r="133">
       <c r="A133" s="2">
@@ -11021,20 +11158,20 @@
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="J133" s="3"/>
       <c r="K133" s="2">
@@ -11045,15 +11182,15 @@
       </c>
       <c r="M133" s="3"/>
       <c r="N133" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O133" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P133" s="3"/>
       <c r="Q133" s="3"/>
       <c r="R133" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S133" s="4" t="b">
         <v>1</v>
@@ -11081,52 +11218,19 @@
       <c r="AH133" s="4" t="b">
         <v>0</v>
       </c>
+      <c r="AI133" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="289">
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="O88:Q88"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="O81:P81"/>
+    <mergeCell ref="O82:P82"/>
+    <mergeCell ref="O83:P83"/>
+    <mergeCell ref="O84:P84"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="O86:P86"/>
+    <mergeCell ref="O87:P87"/>
     <mergeCell ref="O16:Q16"/>
     <mergeCell ref="O17:Q17"/>
     <mergeCell ref="O18:P18"/>
@@ -11134,120 +11238,8 @@
     <mergeCell ref="O20:Q20"/>
     <mergeCell ref="O21:Q21"/>
     <mergeCell ref="O22:P22"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="I64:J64"/>
-    <mergeCell ref="I65:J65"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="I68:J68"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="I120:J120"/>
-    <mergeCell ref="I122:J122"/>
-    <mergeCell ref="I126:J126"/>
-    <mergeCell ref="I127:J127"/>
-    <mergeCell ref="I128:J128"/>
-    <mergeCell ref="I131:J131"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="I104:J104"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="I110:J110"/>
-    <mergeCell ref="I111:J111"/>
-    <mergeCell ref="I116:J116"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="I62:J62"/>
-    <mergeCell ref="O88:Q88"/>
-    <mergeCell ref="O89:P89"/>
-    <mergeCell ref="O92:P92"/>
-    <mergeCell ref="O93:Q93"/>
-    <mergeCell ref="O94:Q94"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="O98:P98"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="O100:P100"/>
-    <mergeCell ref="O101:Q101"/>
-    <mergeCell ref="O102:P102"/>
-    <mergeCell ref="O103:P103"/>
-    <mergeCell ref="O104:Q104"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="O106:P106"/>
-    <mergeCell ref="O107:P107"/>
-    <mergeCell ref="O108:Q108"/>
-    <mergeCell ref="O111:P111"/>
-    <mergeCell ref="O112:Q112"/>
-    <mergeCell ref="O114:P114"/>
-    <mergeCell ref="O115:P115"/>
-    <mergeCell ref="O123:P123"/>
-    <mergeCell ref="O124:Q124"/>
-    <mergeCell ref="O125:P125"/>
-    <mergeCell ref="O126:P126"/>
-    <mergeCell ref="O128:P128"/>
-    <mergeCell ref="O129:P129"/>
-    <mergeCell ref="O130:P130"/>
-    <mergeCell ref="O132:Q132"/>
-    <mergeCell ref="O116:P116"/>
-    <mergeCell ref="O117:P117"/>
-    <mergeCell ref="O118:P118"/>
-    <mergeCell ref="O119:P119"/>
-    <mergeCell ref="O120:P120"/>
-    <mergeCell ref="O121:P121"/>
-    <mergeCell ref="O122:P122"/>
     <mergeCell ref="O23:P23"/>
     <mergeCell ref="O24:P24"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="O26:P26"/>
     <mergeCell ref="O27:P27"/>
     <mergeCell ref="O28:P28"/>
     <mergeCell ref="O29:Q29"/>
@@ -11258,6 +11250,8 @@
     <mergeCell ref="O34:Q34"/>
     <mergeCell ref="O36:P36"/>
     <mergeCell ref="O37:P37"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="O39:P39"/>
     <mergeCell ref="O40:Q40"/>
     <mergeCell ref="O41:P41"/>
     <mergeCell ref="O42:Q42"/>
@@ -11286,15 +11280,230 @@
     <mergeCell ref="O76:P76"/>
     <mergeCell ref="O79:P79"/>
     <mergeCell ref="O80:P80"/>
-    <mergeCell ref="O81:P81"/>
-    <mergeCell ref="O82:P82"/>
-    <mergeCell ref="O83:P83"/>
-    <mergeCell ref="O84:P84"/>
-    <mergeCell ref="O85:P85"/>
-    <mergeCell ref="O86:P86"/>
-    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="I110:J110"/>
+    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="I116:J116"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="I120:J120"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="I126:J126"/>
+    <mergeCell ref="I127:J127"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="I122:J122"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="I128:J128"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="O92:P92"/>
+    <mergeCell ref="O93:Q93"/>
+    <mergeCell ref="O94:Q94"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="O98:P98"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="O100:P100"/>
+    <mergeCell ref="O101:Q101"/>
+    <mergeCell ref="O102:P102"/>
+    <mergeCell ref="O103:P103"/>
+    <mergeCell ref="O104:Q104"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="O106:P106"/>
+    <mergeCell ref="O107:P107"/>
+    <mergeCell ref="O108:Q108"/>
+    <mergeCell ref="O111:P111"/>
+    <mergeCell ref="O112:Q112"/>
+    <mergeCell ref="O114:P114"/>
+    <mergeCell ref="O115:P115"/>
+    <mergeCell ref="O116:P116"/>
+    <mergeCell ref="O117:P117"/>
+    <mergeCell ref="O118:P118"/>
+    <mergeCell ref="O119:P119"/>
+    <mergeCell ref="O128:P128"/>
+    <mergeCell ref="O129:P129"/>
+    <mergeCell ref="O130:P130"/>
+    <mergeCell ref="O132:Q132"/>
+    <mergeCell ref="O120:P120"/>
+    <mergeCell ref="O121:P121"/>
+    <mergeCell ref="O122:P122"/>
+    <mergeCell ref="O123:P123"/>
+    <mergeCell ref="O124:Q124"/>
+    <mergeCell ref="O125:P125"/>
+    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F102:G102"/>
     <mergeCell ref="F103:G103"/>
     <mergeCell ref="F104:G104"/>
+    <mergeCell ref="I104:J104"/>
+    <mergeCell ref="I105:J105"/>
     <mergeCell ref="F105:G105"/>
     <mergeCell ref="F106:G106"/>
     <mergeCell ref="F107:G107"/>
@@ -11302,77 +11511,6 @@
     <mergeCell ref="F109:G109"/>
     <mergeCell ref="F110:G110"/>
     <mergeCell ref="F111:G111"/>
-    <mergeCell ref="F112:G112"/>
-    <mergeCell ref="F113:G113"/>
-    <mergeCell ref="F114:G114"/>
-    <mergeCell ref="F115:G115"/>
-    <mergeCell ref="F116:G116"/>
-    <mergeCell ref="F117:G117"/>
-    <mergeCell ref="F118:G118"/>
-    <mergeCell ref="F119:G119"/>
-    <mergeCell ref="F120:G120"/>
-    <mergeCell ref="F121:G121"/>
-    <mergeCell ref="F122:G122"/>
-    <mergeCell ref="F123:G123"/>
-    <mergeCell ref="F131:G131"/>
-    <mergeCell ref="F132:G132"/>
-    <mergeCell ref="F133:G133"/>
-    <mergeCell ref="F124:G124"/>
-    <mergeCell ref="F125:G125"/>
-    <mergeCell ref="F126:G126"/>
-    <mergeCell ref="F127:G127"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="F129:G129"/>
-    <mergeCell ref="F130:G130"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="F92:G92"/>
-    <mergeCell ref="F93:G93"/>
-    <mergeCell ref="F94:G94"/>
-    <mergeCell ref="F95:G95"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F102:G102"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
